--- a/docs/game/collections-zh_CN.xlsx
+++ b/docs/game/collections-zh_CN.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
   <si>
     <t>藏品</t>
   </si>
@@ -205,6 +205,9 @@
     <t>里面装有灯芯的南瓜，上面还雕刻着“可怕”的表情。</t>
   </si>
   <si>
+    <t>你耗时已长</t>
+  </si>
+  <si>
     <t>放大镜</t>
   </si>
   <si>
@@ -220,19 +223,10 @@
     <t>水晶球</t>
   </si>
   <si>
-    <t>一颗晶莹剔透的水晶球，在内部留住了一片冬景。</t>
-  </si>
-  <si>
-    <t>仔细看去，这个雪人正在向你招手！</t>
-  </si>
-  <si>
-    <t>奖杯</t>
-  </si>
-  <si>
-    <t>这是属于你的荣耀！</t>
-  </si>
-  <si>
-    <t>奖杯底座上刻着一行小字：最佳钓鱼佬奖。</t>
+    <t>一颗晶莹剔透的水晶球，在内部留住了一串圣诞的记忆。</t>
+  </si>
+  <si>
+    <t>这棵圣诞树好像在向你招手</t>
   </si>
   <si>
     <t>书签</t>
@@ -1190,7 +1184,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12.0909090909091" customWidth="1"/>
@@ -1470,68 +1464,68 @@
       <c r="C22" t="s">
         <v>57</v>
       </c>
+      <c r="D22" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B25" t="s">
         <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B27" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1545,19 +1539,8 @@
       <c r="C28" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
+      <c r="D28" t="s">
         <v>73</v>
-      </c>
-      <c r="B29" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/docs/game/collections-zh_CN.xlsx
+++ b/docs/game/collections-zh_CN.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="69">
   <si>
     <t>藏品</t>
   </si>
@@ -76,7 +76,7 @@
     <t>瓶中船</t>
   </si>
   <si>
-    <t>桨儿桨儿看不见，船上也没帆。飘啊飘啊，飘到心间……</t>
+    <t>小船儿轻轻飘向远方，飘啊飘啊，飘到心间……</t>
   </si>
   <si>
     <t>这艘船正在缓缓行驶，驶向远方。</t>
@@ -236,21 +236,6 @@
   </si>
   <si>
     <t>这个书签标记了你水塘生活的瞬间。</t>
-  </si>
-  <si>
-    <t>舞蹈八音盒</t>
-  </si>
-  <si>
-    <t>上了发条之后，便会演奏优美的音乐，表演轻盈的舞蹈。</t>
-  </si>
-  <si>
-    <t>胡桃夹子</t>
-  </si>
-  <si>
-    <t>忠诚的士兵。</t>
-  </si>
-  <si>
-    <t>他仍然保卫着你。</t>
   </si>
 </sst>
 </file>
@@ -1184,7 +1169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12.0909090909091" customWidth="1"/>
@@ -1516,31 +1501,6 @@
       </c>
       <c r="D26" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
-        <v>69</v>
-      </c>
-      <c r="B27" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" t="s">
-        <v>72</v>
-      </c>
-      <c r="D28" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/docs/game/collections-zh_CN.xlsx
+++ b/docs/game/collections-zh_CN.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="71">
   <si>
     <t>藏品</t>
   </si>
@@ -236,6 +236,12 @@
   </si>
   <si>
     <t>这个书签标记了你水塘生活的瞬间。</t>
+  </si>
+  <si>
+    <t>八音盒</t>
+  </si>
+  <si>
+    <t>朴实而神奇的小盒，转动把手就能奏出美妙的乐曲。</t>
   </si>
 </sst>
 </file>
@@ -1169,7 +1175,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="12.0909090909091" customWidth="1"/>
@@ -1501,6 +1507,17 @@
       </c>
       <c r="D26" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
